--- a/04_DESIGN_TABLES/DesignTable_0304.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0304.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 0304 Standard Nut (JIC 37deg tube nut) - Design Table v1 | AW s43 double-pass 9 rows | single-source | GENERATED 2026-09-23</t>
+          <t>OMi 0304 Standard Nut (JIC 37deg tube nut) - Design Table v1 | AW s43 double-pass 9 rows | single-source | GENERATED 2026-09-23 | 2026-10-02 (group NUTS-CAPS): OMi BUILD rows filled from the OMi dimension file (one source with Brennan, ASSUMED)</t>
         </is>
       </c>
     </row>
@@ -945,24 +945,43 @@
           <t>0304-C-02</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>0304-C-02</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5/16-24 UNF</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 4 (0304-C-02): Overall Length 0.50 = cap length (catalog L LGTH), Hex Flat 0.375, Side 1 Thread 5/16-24 UNF, Side 1 Size 1/8" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.500, C HEX 0.375, B1 THREAD 5/16-24, TUBE O.D. 1/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; NOT BUILT YET (geometry, not data): no Brennan STEP with a female -02 JIC port (thread depth + 37deg seat) in 09_STEP_FILES (needs BRENNAN_0304-C-02.stp); the generator skips this row until the -02 port is measured; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -982,24 +1001,43 @@
           <t>0304-C-03</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>0304-C-03</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3/8-24 UNF</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 5 (0304-C-03): Overall Length 0.56 = cap length (catalog L LGTH), Hex Flat 0.438, Side 1 Thread 3/8-24 UNF, Side 1 Size 3/16" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.562, C HEX 0.438, B1 THREAD 3/8-24, TUBE O.D. 3/16 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.56 vs Brennan catalog 0.562: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1019,24 +1057,43 @@
           <t>0304-C-04</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>0304-C-04</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>7/16-20 UNF</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 6 (0304-C-04): Overall Length 0.59 = cap length (catalog L LGTH), Hex Flat 0.562, Side 1 Thread 7/16-20 UNF, Side 1 Size 1/4" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.594, C HEX 0.562, B1 THREAD 7/16-20, TUBE O.D. 1/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.59 vs Brennan catalog 0.594: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1056,24 +1113,43 @@
           <t>0304-C-05</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>0304-C-05</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1/2-20 UNF</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 7 (0304-C-05): Overall Length 0.61 = cap length (catalog L LGTH), Hex Flat 0.625, Side 1 Thread 1/2-20 UNF, Side 1 Size 5/16" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.609, C HEX 0.625, B1 THREAD 1/2-20, TUBE O.D. 5/16 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.61 vs Brennan catalog 0.609: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1093,24 +1169,43 @@
           <t>0304-C-06</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>0304-C-06</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>9/16-18 UNF</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 8 (0304-C-06): Overall Length 0.63 = cap length (catalog L LGTH), Hex Flat 0.688, Side 1 Thread 9/16-18 UNF, Side 1 Size 3/8" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.625, C HEX 0.687, B1 THREAD 9/16-18, TUBE O.D. 3/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.63 vs Brennan catalog 0.625: rounding only; hex: OMi 0.688 vs Brennan catalog 0.687: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1130,24 +1225,43 @@
           <t>0304-C-08</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0304-C-08</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3/4-16 UNF</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 9 (0304-C-08): Overall Length 0.75 = cap length (catalog L LGTH), Hex Flat 0.875, Side 1 Thread 3/4-16 UNF, Side 1 Size 1/2" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.750, C HEX 0.875, B1 THREAD 3/4-16, TUBE O.D. 1/2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1167,24 +1281,43 @@
           <t>0304-C-10</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>0304-C-10</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7/8-14 UNF</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 10 (0304-C-10): Overall Length 0.84 = cap length (catalog L LGTH), Hex Flat 1.000, Side 1 Thread 7/8-14 UNF, Side 1 Size 5/8" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.844, C HEX 1.000, B1 THREAD 7/8-14, TUBE O.D. 5/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.84 vs Brennan catalog 0.844: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1204,24 +1337,43 @@
           <t>0304-C-12</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>0304-C-12</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1 1/16-12 UNF</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 11 (0304-C-12): Overall Length 0.91 = cap length (catalog L LGTH), Hex Flat 1.250, Side 1 Thread 1 1/16-12 UNF, Side 1 Size 3/4" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.906, C HEX 1.250, B1 THREAD 1 1/16-12, TUBE O.D. 3/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.91 vs Brennan catalog 0.906: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1241,24 +1393,43 @@
           <t>0304-C-14</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>0304-C-14</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UNF</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 12 (0304-C-14): Overall Length 0.97 = cap length (catalog L LGTH), Hex Flat 1.375, Side 1 Thread 1 3/16-12 UNF, Side 1 Size 7/8" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 0.969, C HEX 1.375, B1 THREAD 1-3/16-12, TUBE O.D. 7/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 0.97 vs Brennan catalog 0.969: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1278,24 +1449,43 @@
           <t>0304-C-16</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>0304-C-16</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1 5/16-12 UNF</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 13 (0304-C-16): Overall Length 1.02 = cap length (catalog L LGTH), Hex Flat 1.500, Side 1 Thread 1 5/16-12 UNF, Side 1 Size 1" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 1.016, C HEX 1.500, B1 THREAD 1 5/16-12, TUBE O.D. 1 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 1.02 vs Brennan catalog 1.016: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1315,24 +1505,43 @@
           <t>0304-C-20</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>0304-C-20</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1 5/8-12 UNF</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 14 (0304-C-20): Overall Length 1.06 = cap length (catalog L LGTH), Hex Flat 2.000, Side 1 Thread 1 5/8-12 UNF, Side 1 Size 1 1/4" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 1.062, C HEX 2.000, B1 THREAD 1 5/8-12, TUBE O.D. 1-1/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 1.06 vs Brennan catalog 1.062: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1352,24 +1561,43 @@
           <t>0304-C-24</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0304-C-24</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1 7/8-12 UNF</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 15 (0304-C-24): Overall Length 1.19 = cap length (catalog L LGTH), Hex Flat 2.250, Side 1 Thread 1 7/8-12 UNF, Side 1 Size 1 1/2" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 1.188, C HEX 2.250, B1 THREAD 1-7/8-12, TUBE O.D. 1-1/2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): length: OMi 1.19 vs Brennan catalog 1.188: rounding only; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1389,24 +1617,43 @@
           <t>0304-C-32</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0304-C-32</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2 1/2-12 UNF</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>L / CHEX / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 16 (0304-C-32): Overall Length 1.44 = cap length (catalog L LGTH), Hex Flat 2.875, Side 1 Thread 2 1/2-12 UNF, Side 1 Size 2" (column mapping Q-B-OTHER-0304 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t01, page-verified): L LGTH 1.440, C HEX 2.880, B1 THREAD 2 1/2-12, TUBE O.D. 2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC cap nut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): cap pocket bottom 0.050 below the seat end (BRENNAN_0304-C-08) and the female JIC cavity per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): hex: OMi 2.875 vs Brennan catalog 2.880 - DIFFER by 0.005; OMi used (OMi first, user decision 2026-09-25); the catalog hex 2.880 is most likely 2.88 padded (every other -32 nut hex in the catalog prints 2.875; MS51531D / AN818 -32 nut hex 2.875); single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
